--- a/input.xlsx
+++ b/input.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\223028173.HCAD\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ryanj\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B80C9DA-0EEF-4E03-A38B-B1452A42CBCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35E8FF15-0B91-4D5D-B9BE-4F3204DA1C0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Metadata" sheetId="1" r:id="rId1"/>
@@ -110,81 +110,18 @@
     <t>https://www.gehealthcare.com/about/newsroom</t>
   </si>
   <si>
-    <t>https://www.gehealthcare.co.uk/</t>
-  </si>
-  <si>
     <t>UK</t>
   </si>
   <si>
-    <t>https://www.gehealthcare.co.uk/products/imaging</t>
-  </si>
-  <si>
-    <t>https://www.gehealthcare.co.uk/products/computed-tomography</t>
-  </si>
-  <si>
-    <t>https://www.gehealthcare.co.uk/products/ultrasound</t>
-  </si>
-  <si>
-    <t>https://www.gehealthcare.co.uk/products/ultrasound/voluson</t>
-  </si>
-  <si>
-    <t>https://www.gehealthcare.co.uk/specialties/patient-care-solutions</t>
-  </si>
-  <si>
-    <t>https://www.gehealthcare.co.uk/products/patient-monitoring</t>
-  </si>
-  <si>
-    <t>https://www.gehealthcare.co.uk/products/molecular-imaging-agents</t>
-  </si>
-  <si>
-    <t>https://www.gehealthcare.co.uk/products/molecular-imaging-agents/datscan</t>
-  </si>
-  <si>
-    <t>https://www.gehealthcare.co.uk/products/contrast-media</t>
-  </si>
-  <si>
-    <t>https://www.gehealthcare.co.uk/products/contrast-media/gadobutrol</t>
-  </si>
-  <si>
-    <t>https://www.gehealthcare.co.uk/insights</t>
-  </si>
-  <si>
-    <t>https://www.gehealthcare.de/</t>
-  </si>
-  <si>
     <t>DE</t>
   </si>
   <si>
     <t>TC-01,TC-02,TC-03,TC-04,TC-05,TC-06,TC-13,TC-09,TC-14</t>
   </si>
   <si>
-    <t>https://www.gehealthcare.de/products/imaging</t>
-  </si>
-  <si>
-    <t>https://www.gehealthcare.de/products/patient-monitoring</t>
-  </si>
-  <si>
-    <t>https://www.gehealthcare.de/products/contrast-media</t>
-  </si>
-  <si>
-    <t>https://www.gehealthcare.de/products/contrast-media/omnipaque</t>
-  </si>
-  <si>
     <t>TC-03,TC-04,TC-05,TC-06,TC-12,TC-09,TC-14</t>
   </si>
   <si>
-    <t>https://www.gehealthcare.de/products/nuclear-imaging-agents</t>
-  </si>
-  <si>
-    <t>https://www.gehealthcare.de/products/nuclear-imaging-agents/datscan</t>
-  </si>
-  <si>
-    <t>https://www.gehealthcare.de/insights/articles</t>
-  </si>
-  <si>
-    <t>https://www.gehealthcare.de/insights/news</t>
-  </si>
-  <si>
     <t>https://www.gehealthcare.fr/</t>
   </si>
   <si>
@@ -285,6 +222,69 @@
   </si>
   <si>
     <t>HTTP Status</t>
+  </si>
+  <si>
+    <t>https://www.gehealthcare.com/en-gb/</t>
+  </si>
+  <si>
+    <t>https://www.gehealthcare.com/en-gb/products/imaging</t>
+  </si>
+  <si>
+    <t>https://www.gehealthcare.com/en-gb/products/computed-tomography</t>
+  </si>
+  <si>
+    <t>https://www.gehealthcare.com/en-gb/products/ultrasound</t>
+  </si>
+  <si>
+    <t>https://www.gehealthcare.com/en-gb/products/ultrasound/voluson</t>
+  </si>
+  <si>
+    <t>https://www.gehealthcare.com/en-gb/specialties/patient-care-solutions</t>
+  </si>
+  <si>
+    <t>https://www.gehealthcare.com/en-gb/products/patient-monitoring</t>
+  </si>
+  <si>
+    <t>https://www.gehealthcare.com/en-gb/products/molecular-imaging-agents</t>
+  </si>
+  <si>
+    <t>https://www.gehealthcare.com/en-gb/products/molecular-imaging-agents/datscan</t>
+  </si>
+  <si>
+    <t>https://www.gehealthcare.com/en-gb/products/contrast-media</t>
+  </si>
+  <si>
+    <t>https://www.gehealthcare.com/en-gb/products/contrast-media/gadobutrol</t>
+  </si>
+  <si>
+    <t>https://www.gehealthcare.com/en-gb/insights</t>
+  </si>
+  <si>
+    <t>https://www.gehealthcare.com/de-de/</t>
+  </si>
+  <si>
+    <t>https://www.gehealthcare.com/de-de/products/imaging</t>
+  </si>
+  <si>
+    <t>https://www.gehealthcare.com/de-de/products/patient-monitoring</t>
+  </si>
+  <si>
+    <t>https://www.gehealthcare.com/de-de/products/contrast-media</t>
+  </si>
+  <si>
+    <t>https://www.gehealthcare.com/de-de/products/contrast-media/omnipaque</t>
+  </si>
+  <si>
+    <t>https://www.gehealthcare.com/de-de/products/nuclear-imaging-agents</t>
+  </si>
+  <si>
+    <t>https://www.gehealthcare.com/de-de/products/nuclear-imaging-agents/datscan</t>
+  </si>
+  <si>
+    <t>https://www.gehealthcare.com/de-de/insights/articles</t>
+  </si>
+  <si>
+    <t>https://www.gehealthcare.com/de-de/insights/news</t>
   </si>
 </sst>
 </file>
@@ -320,10 +320,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -893,11 +894,11 @@
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="A15" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B15" t="s">
         <v>27</v>
-      </c>
-      <c r="B15" t="s">
-        <v>28</v>
       </c>
       <c r="C15" t="s">
         <v>9</v>
@@ -905,10 +906,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>29</v>
+        <v>66</v>
       </c>
       <c r="B16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C16" t="s">
         <v>11</v>
@@ -916,10 +917,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>30</v>
+        <v>67</v>
       </c>
       <c r="B17" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C17" t="s">
         <v>13</v>
@@ -927,10 +928,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>31</v>
+        <v>68</v>
       </c>
       <c r="B18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C18" t="s">
         <v>15</v>
@@ -938,10 +939,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>32</v>
+        <v>69</v>
       </c>
       <c r="B19" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C19" t="s">
         <v>13</v>
@@ -949,10 +950,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>33</v>
+        <v>70</v>
       </c>
       <c r="B20" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C20" t="s">
         <v>15</v>
@@ -960,10 +961,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="B21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C21" t="s">
         <v>13</v>
@@ -971,10 +972,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>35</v>
+        <v>72</v>
       </c>
       <c r="B22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C22" t="s">
         <v>20</v>
@@ -982,10 +983,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>36</v>
+        <v>73</v>
       </c>
       <c r="B23" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C23" t="s">
         <v>20</v>
@@ -993,10 +994,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>37</v>
+        <v>74</v>
       </c>
       <c r="B24" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C24" t="s">
         <v>20</v>
@@ -1004,10 +1005,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="B25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C25" t="s">
         <v>20</v>
@@ -1015,10 +1016,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>39</v>
+        <v>76</v>
       </c>
       <c r="B26" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C26" t="s">
         <v>25</v>
@@ -1026,21 +1027,21 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>40</v>
+        <v>77</v>
       </c>
       <c r="B27" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="C27" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>43</v>
+        <v>78</v>
       </c>
       <c r="B28" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="C28" t="s">
         <v>11</v>
@@ -1048,10 +1049,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>44</v>
+        <v>79</v>
       </c>
       <c r="B29" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="C29" t="s">
         <v>11</v>
@@ -1059,10 +1060,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B30" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="C30" t="s">
         <v>11</v>
@@ -1070,21 +1071,21 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B31" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="C31" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>48</v>
+        <v>82</v>
       </c>
       <c r="B32" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="C32" t="s">
         <v>11</v>
@@ -1092,21 +1093,21 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>49</v>
+        <v>83</v>
       </c>
       <c r="B33" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="C33" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="B34" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="C34" t="s">
         <v>25</v>
@@ -1114,10 +1115,10 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="B35" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="C35" t="s">
         <v>25</v>
@@ -1125,10 +1126,10 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="B36" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="C36" t="s">
         <v>9</v>
@@ -1136,10 +1137,10 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="B37" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="C37" t="s">
         <v>11</v>
@@ -1147,10 +1148,10 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="B38" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="C38" t="s">
         <v>13</v>
@@ -1158,10 +1159,10 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="B39" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="C39" t="s">
         <v>11</v>
@@ -1169,10 +1170,10 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="B40" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="C40" t="s">
         <v>11</v>
@@ -1180,10 +1181,10 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="B41" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="C41" t="s">
         <v>9</v>
@@ -1191,10 +1192,10 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="C42" t="s">
         <v>11</v>
@@ -1202,10 +1203,10 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="C43" t="s">
         <v>13</v>
@@ -1213,10 +1214,10 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="C44" t="s">
         <v>11</v>
@@ -1224,10 +1225,10 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="C45" t="s">
         <v>13</v>
@@ -1235,10 +1236,10 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="C46" t="s">
         <v>11</v>
@@ -1246,10 +1247,10 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="C47" t="s">
         <v>11</v>
@@ -1257,10 +1258,10 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="C48" t="s">
         <v>25</v>
@@ -1268,10 +1269,10 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="B49" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="C49" t="s">
         <v>25</v>
@@ -1279,10 +1280,10 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="B50" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="C50" t="s">
         <v>11</v>
@@ -1290,10 +1291,10 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>69</v>
+        <v>48</v>
       </c>
       <c r="B51" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="C51" t="s">
         <v>11</v>
@@ -1322,52 +1323,52 @@
         <v>4</v>
       </c>
       <c r="B1" t="s">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="C1" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="D1" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="E1" t="s">
-        <v>73</v>
+        <v>52</v>
       </c>
       <c r="F1" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="G1" t="s">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="H1" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="I1" t="s">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="J1" t="s">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="K1" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="L1" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="M1" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="N1" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="O1" t="s">
-        <v>83</v>
+        <v>62</v>
       </c>
       <c r="P1" t="s">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="Q1" t="s">
-        <v>85</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>

--- a/input.xlsx
+++ b/input.xlsx
@@ -1,33 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ryanj\Desktop\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35E8FF15-0B91-4D5D-B9BE-4F3204DA1C0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Metadata" sheetId="1" r:id="rId1"/>
-    <sheet name="URLs" sheetId="2" r:id="rId2"/>
-    <sheet name="Results" sheetId="3" r:id="rId3"/>
+    <sheet sheetId="1" name="Metadata" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="URLs" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="Results" state="visible" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
-  <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="85">
   <si>
     <t>Run Date</t>
   </si>
@@ -110,18 +99,78 @@
     <t>https://www.gehealthcare.com/about/newsroom</t>
   </si>
   <si>
+    <t>https://www.gehealthcare.com/en-gb/</t>
+  </si>
+  <si>
     <t>UK</t>
   </si>
   <si>
+    <t>https://www.gehealthcare.com/en-gb/products/imaging</t>
+  </si>
+  <si>
+    <t>https://www.gehealthcare.com/en-gb/products/computed-tomography</t>
+  </si>
+  <si>
+    <t>https://www.gehealthcare.com/en-gb/products/ultrasound</t>
+  </si>
+  <si>
+    <t>https://www.gehealthcare.com/en-gb/products/ultrasound/voluson</t>
+  </si>
+  <si>
+    <t>https://www.gehealthcare.com/en-gb/specialties/patient-care-solutions</t>
+  </si>
+  <si>
+    <t>https://www.gehealthcare.com/en-gb/products/patient-monitoring</t>
+  </si>
+  <si>
+    <t>https://www.gehealthcare.com/en-gb/products/molecular-imaging-agents</t>
+  </si>
+  <si>
+    <t>https://www.gehealthcare.com/en-gb/products/molecular-imaging-agents/datscan</t>
+  </si>
+  <si>
+    <t>https://www.gehealthcare.com/en-gb/products/contrast-media</t>
+  </si>
+  <si>
+    <t>https://www.gehealthcare.com/en-gb/products/contrast-media/gadobutrol</t>
+  </si>
+  <si>
+    <t>https://www.gehealthcare.com/en-gb/insights</t>
+  </si>
+  <si>
+    <t>https://www.gehealthcare.com/de-de/</t>
+  </si>
+  <si>
     <t>DE</t>
   </si>
   <si>
     <t>TC-01,TC-02,TC-03,TC-04,TC-05,TC-06,TC-13,TC-09,TC-14</t>
   </si>
   <si>
+    <t>https://www.gehealthcare.com/de-de/products/imaging</t>
+  </si>
+  <si>
+    <t>https://www.gehealthcare.com/de-de/products/patient-monitoring</t>
+  </si>
+  <si>
+    <t>https://www.gehealthcare.com/de-de/products/contrast-media</t>
+  </si>
+  <si>
+    <t>https://www.gehealthcare.com/de-de/products/contrast-media/omnipaque</t>
+  </si>
+  <si>
     <t>TC-03,TC-04,TC-05,TC-06,TC-12,TC-09,TC-14</t>
   </si>
   <si>
+    <t>https://www.gehealthcare.com/de-de/products/nuclear-imaging-agents</t>
+  </si>
+  <si>
+    <t>https://www.gehealthcare.com/de-de/products/nuclear-imaging-agents/datscan</t>
+  </si>
+  <si>
+    <t>https://www.gehealthcare.com/de-de/insights/articles</t>
+  </si>
+  <si>
     <t>https://www.gehealthcare.fr/</t>
   </si>
   <si>
@@ -222,82 +271,26 @@
   </si>
   <si>
     <t>HTTP Status</t>
-  </si>
-  <si>
-    <t>https://www.gehealthcare.com/en-gb/</t>
-  </si>
-  <si>
-    <t>https://www.gehealthcare.com/en-gb/products/imaging</t>
-  </si>
-  <si>
-    <t>https://www.gehealthcare.com/en-gb/products/computed-tomography</t>
-  </si>
-  <si>
-    <t>https://www.gehealthcare.com/en-gb/products/ultrasound</t>
-  </si>
-  <si>
-    <t>https://www.gehealthcare.com/en-gb/products/ultrasound/voluson</t>
-  </si>
-  <si>
-    <t>https://www.gehealthcare.com/en-gb/specialties/patient-care-solutions</t>
-  </si>
-  <si>
-    <t>https://www.gehealthcare.com/en-gb/products/patient-monitoring</t>
-  </si>
-  <si>
-    <t>https://www.gehealthcare.com/en-gb/products/molecular-imaging-agents</t>
-  </si>
-  <si>
-    <t>https://www.gehealthcare.com/en-gb/products/molecular-imaging-agents/datscan</t>
-  </si>
-  <si>
-    <t>https://www.gehealthcare.com/en-gb/products/contrast-media</t>
-  </si>
-  <si>
-    <t>https://www.gehealthcare.com/en-gb/products/contrast-media/gadobutrol</t>
-  </si>
-  <si>
-    <t>https://www.gehealthcare.com/en-gb/insights</t>
-  </si>
-  <si>
-    <t>https://www.gehealthcare.com/de-de/</t>
-  </si>
-  <si>
-    <t>https://www.gehealthcare.com/de-de/products/imaging</t>
-  </si>
-  <si>
-    <t>https://www.gehealthcare.com/de-de/products/patient-monitoring</t>
-  </si>
-  <si>
-    <t>https://www.gehealthcare.com/de-de/products/contrast-media</t>
-  </si>
-  <si>
-    <t>https://www.gehealthcare.com/de-de/products/contrast-media/omnipaque</t>
-  </si>
-  <si>
-    <t>https://www.gehealthcare.com/de-de/products/nuclear-imaging-agents</t>
-  </si>
-  <si>
-    <t>https://www.gehealthcare.com/de-de/products/nuclear-imaging-agents/datscan</t>
-  </si>
-  <si>
-    <t>https://www.gehealthcare.com/de-de/insights/articles</t>
-  </si>
-  <si>
-    <t>https://www.gehealthcare.com/de-de/insights/news</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
       <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <charset val="1"/>
       <color theme="1"/>
+      <family val="2"/>
+      <sz val="11"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -322,34 +315,14 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="22" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="6">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -390,76 +363,28 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF9C0006"/>
-      <rgbColor rgb="FF006100"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFC6EFCE"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFC7CE"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF333333"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -472,50 +397,76 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="tblMetadata" displayName="tblMetadata" ref="A1:D2" totalsRowShown="0">
-  <autoFilter ref="A1:D2" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" name="tblMetadata" displayName="tblMetadata" ref="A1:D2" totalsRowShown="1" headerRowCount="0">
+  <autoFilter ref="A1:D2">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+    <filterColumn colId="3" hiddenButton="1"/>
+  </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Run Date"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Run Time"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Initiated by"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Notes"/>
+    <tableColumn id="1" name="Run Date"/>
+    <tableColumn id="2" name="Run Time"/>
+    <tableColumn id="3" name="Initiated by"/>
+    <tableColumn id="4" name="Notes"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="tblURLs" displayName="tblURLs" ref="A1:B51" totalsRowShown="0">
-  <autoFilter ref="A1:B51" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" name="tblURLs" displayName="tblURLs" ref="A1:B51" totalsRowShown="1" headerRowCount="0">
+  <autoFilter ref="A1:B51">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+  </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="URL"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Region"/>
+    <tableColumn id="1" name="URL"/>
+    <tableColumn id="2" name="Region"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="tblResults" displayName="tblResults" ref="A1:Q51" totalsRowShown="0">
-  <autoFilter ref="A1:Q51" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" name="tblResults" displayName="tblResults" ref="A1:Q51" totalsRowShown="1" headerRowCount="0">
+  <autoFilter ref="A1:Q51">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+    <filterColumn colId="3" hiddenButton="1"/>
+    <filterColumn colId="4" hiddenButton="1"/>
+    <filterColumn colId="5" hiddenButton="1"/>
+    <filterColumn colId="6" hiddenButton="1"/>
+    <filterColumn colId="7" hiddenButton="1"/>
+    <filterColumn colId="8" hiddenButton="1"/>
+    <filterColumn colId="9" hiddenButton="1"/>
+    <filterColumn colId="10" hiddenButton="1"/>
+    <filterColumn colId="11" hiddenButton="1"/>
+    <filterColumn colId="12" hiddenButton="1"/>
+    <filterColumn colId="13" hiddenButton="1"/>
+    <filterColumn colId="14" hiddenButton="1"/>
+    <filterColumn colId="15" hiddenButton="1"/>
+    <filterColumn colId="16" hiddenButton="1"/>
+  </autoFilter>
   <tableColumns count="17">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="URL"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="TC-01"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="TC-02"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="TC-03"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="TC-04"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="TC-05"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="TC-06"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="TC-07"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0200-000009000000}" name="TC-08"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0200-00000A000000}" name="TC-09"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0200-00000B000000}" name="TC-10"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0200-00000C000000}" name="TC-11"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0200-00000D000000}" name="TC-12"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0200-00000E000000}" name="TC-13"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0200-00000F000000}" name="TC-14"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0200-000010000000}" name="Page Pass?"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0200-000011000000}" name="HTTP Status"/>
+    <tableColumn id="1" name="URL"/>
+    <tableColumn id="2" name="TC-01"/>
+    <tableColumn id="3" name="TC-02"/>
+    <tableColumn id="4" name="TC-03"/>
+    <tableColumn id="5" name="TC-04"/>
+    <tableColumn id="6" name="TC-05"/>
+    <tableColumn id="7" name="TC-06"/>
+    <tableColumn id="8" name="TC-07"/>
+    <tableColumn id="9" name="TC-08"/>
+    <tableColumn id="10" name="TC-09"/>
+    <tableColumn id="11" name="TC-10"/>
+    <tableColumn id="12" name="TC-11"/>
+    <tableColumn id="13" name="TC-12"/>
+    <tableColumn id="14" name="TC-13"/>
+    <tableColumn id="15" name="TC-14"/>
+    <tableColumn id="16" name="Page Pass?"/>
+    <tableColumn id="17" name="HTTP Status"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -696,9 +647,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" defaultColWidth="8.85546875"/>
   <cols>
     <col min="1" max="4" width="16.7109375" customWidth="1"/>
   </cols>
@@ -717,13 +668,13 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
@@ -731,9 +682,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C51"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C50"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" defaultColWidth="8.85546875"/>
   <cols>
     <col min="1" max="1" width="45.7109375" customWidth="1"/>
     <col min="2" max="2" width="12.7109375" customWidth="1"/>
@@ -895,10 +846,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="B15" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C15" t="s">
         <v>9</v>
@@ -906,10 +857,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>66</v>
+        <v>29</v>
       </c>
       <c r="B16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C16" t="s">
         <v>11</v>
@@ -917,10 +868,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>67</v>
+        <v>30</v>
       </c>
       <c r="B17" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C17" t="s">
         <v>13</v>
@@ -928,10 +879,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>68</v>
+        <v>31</v>
       </c>
       <c r="B18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C18" t="s">
         <v>15</v>
@@ -939,10 +890,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>69</v>
+        <v>32</v>
       </c>
       <c r="B19" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C19" t="s">
         <v>13</v>
@@ -950,10 +901,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>70</v>
+        <v>33</v>
       </c>
       <c r="B20" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C20" t="s">
         <v>15</v>
@@ -961,10 +912,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>71</v>
+        <v>34</v>
       </c>
       <c r="B21" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C21" t="s">
         <v>13</v>
@@ -972,10 +923,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>72</v>
+        <v>35</v>
       </c>
       <c r="B22" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C22" t="s">
         <v>20</v>
@@ -983,10 +934,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>73</v>
+        <v>36</v>
       </c>
       <c r="B23" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C23" t="s">
         <v>20</v>
@@ -994,10 +945,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>74</v>
+        <v>37</v>
       </c>
       <c r="B24" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C24" t="s">
         <v>20</v>
@@ -1005,10 +956,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="B25" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C25" t="s">
         <v>20</v>
@@ -1016,10 +967,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>76</v>
+        <v>39</v>
       </c>
       <c r="B26" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C26" t="s">
         <v>25</v>
@@ -1027,21 +978,21 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>77</v>
+        <v>40</v>
       </c>
       <c r="B27" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="C27" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>78</v>
+        <v>43</v>
       </c>
       <c r="B28" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="C28" t="s">
         <v>11</v>
@@ -1049,10 +1000,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>79</v>
+        <v>44</v>
       </c>
       <c r="B29" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="C29" t="s">
         <v>11</v>
@@ -1060,10 +1011,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="B30" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="C30" t="s">
         <v>11</v>
@@ -1071,21 +1022,21 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>81</v>
+        <v>46</v>
       </c>
       <c r="B31" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="C31" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="B32" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="C32" t="s">
         <v>11</v>
@@ -1093,21 +1044,21 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>83</v>
+        <v>49</v>
       </c>
       <c r="B33" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="C33" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="B34" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="C34" t="s">
         <v>25</v>
@@ -1115,54 +1066,54 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>85</v>
+        <v>51</v>
       </c>
       <c r="B35" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="C35" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="B36" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="C36" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="B37" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="C37" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="B38" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="C38" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="B39" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="C39" t="s">
         <v>11</v>
@@ -1170,76 +1121,76 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="B40" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="C40" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="B41" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="C41" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="B42" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="C42" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="B43" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="C43" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="B44" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="C44" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="B45" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="C45" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="B46" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="C46" t="s">
         <v>11</v>
@@ -1247,21 +1198,21 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="B47" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="C47" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="B48" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="C48" t="s">
         <v>25</v>
@@ -1269,40 +1220,29 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="B49" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="C49" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="B50" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="C50" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>48</v>
-      </c>
-      <c r="B51" t="s">
-        <v>38</v>
-      </c>
-      <c r="C51" t="s">
         <v>11</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
@@ -1310,9 +1250,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Q1"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" defaultColWidth="8.85546875"/>
   <cols>
     <col min="1" max="1" width="42.42578125" customWidth="1"/>
     <col min="2" max="17" width="16.7109375" customWidth="1"/>
@@ -1323,79 +1263,79 @@
         <v>4</v>
       </c>
       <c r="B1" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="C1" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="D1" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="E1" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="F1" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="G1" t="s">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="H1" t="s">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="I1" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="J1" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="K1" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="L1" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="M1" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="N1" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="O1" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="P1" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="Q1" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:M1 B2:P1048576">
-    <cfRule type="containsText" dxfId="5" priority="2" operator="containsText" text="Fail">
+    <cfRule type="containsText" dxfId="0" priority="2">
       <formula>NOT(ISERROR(SEARCH("Fail",B1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="PASS">
+    <cfRule type="containsText" dxfId="1" priority="3">
       <formula>NOT(ISERROR(SEARCH("PASS",B1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="Pass">
+    <cfRule type="containsText" dxfId="2" priority="4">
       <formula>NOT(ISERROR(SEARCH("Pass",B1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="5" operator="containsText" text="FAIL">
+    <cfRule type="containsText" dxfId="3" priority="5">
       <formula>NOT(ISERROR(SEARCH("FAIL",B1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:Q51">
-    <cfRule type="containsText" dxfId="1" priority="6" operator="containsText" text="Pass">
+    <cfRule type="containsText" dxfId="4" priority="6">
       <formula>NOT(ISERROR(SEARCH("Pass",B2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="7" operator="containsText" text="Fail">
+    <cfRule type="containsText" dxfId="5" priority="7">
       <formula>NOT(ISERROR(SEARCH("Fail",B2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>

--- a/input.xlsx
+++ b/input.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="81">
   <si>
     <t>Run Date</t>
   </si>
@@ -151,18 +151,6 @@
   </si>
   <si>
     <t>https://www.gehealthcare.com/de-de/products/patient-monitoring</t>
-  </si>
-  <si>
-    <t>https://www.gehealthcare.com/de-de/products/contrast-media</t>
-  </si>
-  <si>
-    <t>https://www.gehealthcare.com/de-de/products/contrast-media/omnipaque</t>
-  </si>
-  <si>
-    <t>TC-03,TC-04,TC-05,TC-06,TC-12,TC-09,TC-14</t>
-  </si>
-  <si>
-    <t>https://www.gehealthcare.com/de-de/products/nuclear-imaging-agents</t>
   </si>
   <si>
     <t>https://www.gehealthcare.com/de-de/products/nuclear-imaging-agents/datscan</t>
@@ -683,7 +671,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C50"/>
+  <dimension ref="A1:C47"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" defaultColWidth="8.85546875"/>
   <cols>
     <col min="1" max="1" width="45.7109375" customWidth="1"/>
@@ -1028,18 +1016,18 @@
         <v>41</v>
       </c>
       <c r="C31" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>47</v>
+      </c>
+      <c r="B32" t="s">
         <v>48</v>
       </c>
-      <c r="B32" t="s">
-        <v>41</v>
-      </c>
       <c r="C32" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -1047,10 +1035,10 @@
         <v>49</v>
       </c>
       <c r="B33" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="C33" t="s">
-        <v>47</v>
+        <v>11</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -1058,10 +1046,10 @@
         <v>50</v>
       </c>
       <c r="B34" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="C34" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -1069,18 +1057,18 @@
         <v>51</v>
       </c>
       <c r="B35" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C35" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B36" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C36" t="s">
         <v>11</v>
@@ -1088,13 +1076,13 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>53</v>
+      </c>
+      <c r="B37" t="s">
         <v>54</v>
       </c>
-      <c r="B37" t="s">
-        <v>52</v>
-      </c>
       <c r="C37" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -1102,7 +1090,7 @@
         <v>55</v>
       </c>
       <c r="B38" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C38" t="s">
         <v>11</v>
@@ -1113,10 +1101,10 @@
         <v>56</v>
       </c>
       <c r="B39" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C39" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -1124,40 +1112,40 @@
         <v>57</v>
       </c>
       <c r="B40" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C40" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B41" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C41" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B42" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C42" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B43" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C43" t="s">
         <v>11</v>
@@ -1165,32 +1153,32 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B44" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C44" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B45" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C45" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B46" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C46" t="s">
         <v>11</v>
@@ -1198,45 +1186,12 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B47" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C47" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>66</v>
-      </c>
-      <c r="B48" t="s">
-        <v>58</v>
-      </c>
-      <c r="C48" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>67</v>
-      </c>
-      <c r="B49" t="s">
-        <v>58</v>
-      </c>
-      <c r="C49" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>68</v>
-      </c>
-      <c r="B50" t="s">
-        <v>58</v>
-      </c>
-      <c r="C50" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1263,52 +1218,52 @@
         <v>4</v>
       </c>
       <c r="B1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1" t="s">
         <v>69</v>
       </c>
-      <c r="C1" t="s">
+      <c r="G1" t="s">
         <v>70</v>
       </c>
-      <c r="D1" t="s">
+      <c r="H1" t="s">
         <v>71</v>
       </c>
-      <c r="E1" t="s">
+      <c r="I1" t="s">
         <v>72</v>
       </c>
-      <c r="F1" t="s">
+      <c r="J1" t="s">
         <v>73</v>
       </c>
-      <c r="G1" t="s">
+      <c r="K1" t="s">
         <v>74</v>
       </c>
-      <c r="H1" t="s">
+      <c r="L1" t="s">
         <v>75</v>
       </c>
-      <c r="I1" t="s">
+      <c r="M1" t="s">
         <v>76</v>
       </c>
-      <c r="J1" t="s">
+      <c r="N1" t="s">
         <v>77</v>
       </c>
-      <c r="K1" t="s">
+      <c r="O1" t="s">
         <v>78</v>
       </c>
-      <c r="L1" t="s">
+      <c r="P1" t="s">
         <v>79</v>
       </c>
-      <c r="M1" t="s">
+      <c r="Q1" t="s">
         <v>80</v>
-      </c>
-      <c r="N1" t="s">
-        <v>81</v>
-      </c>
-      <c r="O1" t="s">
-        <v>82</v>
-      </c>
-      <c r="P1" t="s">
-        <v>83</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>84</v>
       </c>
     </row>
   </sheetData>

--- a/input.xlsx
+++ b/input.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="85">
   <si>
     <t>Run Date</t>
   </si>
@@ -157,6 +157,18 @@
   </si>
   <si>
     <t>https://www.gehealthcare.com/de-de/insights/articles</t>
+  </si>
+  <si>
+    <t>https://www.gehealthcare.com/de-de/products/nuclear-imaging-agents</t>
+  </si>
+  <si>
+    <t>https://www.gehealthcare.com/de-de/products/ultrasound</t>
+  </si>
+  <si>
+    <t>https://www.gehealthcare.com/de-de/products/computed-tomography</t>
+  </si>
+  <si>
+    <t>https://www.gehealthcare.com/de-de/products/bone-and-metabolic-health</t>
   </si>
   <si>
     <t>https://www.gehealthcare.fr/</t>
@@ -671,7 +683,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C47"/>
+  <dimension ref="A1:C51"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" defaultColWidth="8.85546875"/>
   <cols>
     <col min="1" max="1" width="45.7109375" customWidth="1"/>
@@ -1024,18 +1036,18 @@
         <v>47</v>
       </c>
       <c r="B32" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="C32" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B33" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="C33" t="s">
         <v>11</v>
@@ -1043,10 +1055,10 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B34" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="C34" t="s">
         <v>13</v>
@@ -1054,10 +1066,10 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B35" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="C35" t="s">
         <v>11</v>
@@ -1065,13 +1077,13 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>51</v>
+      </c>
+      <c r="B36" t="s">
         <v>52</v>
       </c>
-      <c r="B36" t="s">
-        <v>48</v>
-      </c>
       <c r="C36" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -1079,40 +1091,40 @@
         <v>53</v>
       </c>
       <c r="B37" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C37" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B38" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C38" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B39" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C39" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B40" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C40" t="s">
         <v>11</v>
@@ -1120,13 +1132,13 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>57</v>
+      </c>
+      <c r="B41" t="s">
         <v>58</v>
       </c>
-      <c r="B41" t="s">
-        <v>54</v>
-      </c>
       <c r="C41" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -1134,7 +1146,7 @@
         <v>59</v>
       </c>
       <c r="B42" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C42" t="s">
         <v>11</v>
@@ -1145,10 +1157,10 @@
         <v>60</v>
       </c>
       <c r="B43" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C43" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -1156,10 +1168,10 @@
         <v>61</v>
       </c>
       <c r="B44" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C44" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -1167,10 +1179,10 @@
         <v>62</v>
       </c>
       <c r="B45" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C45" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -1178,7 +1190,7 @@
         <v>63</v>
       </c>
       <c r="B46" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C46" t="s">
         <v>11</v>
@@ -1189,9 +1201,53 @@
         <v>64</v>
       </c>
       <c r="B47" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C47" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>65</v>
+      </c>
+      <c r="B48" t="s">
+        <v>58</v>
+      </c>
+      <c r="C48" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>66</v>
+      </c>
+      <c r="B49" t="s">
+        <v>58</v>
+      </c>
+      <c r="C49" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>67</v>
+      </c>
+      <c r="B50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C50" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>68</v>
+      </c>
+      <c r="B51" t="s">
+        <v>58</v>
+      </c>
+      <c r="C51" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1218,52 +1274,52 @@
         <v>4</v>
       </c>
       <c r="B1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D1" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="E1" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F1" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G1" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H1" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="I1" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="J1" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="K1" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="L1" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="M1" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="N1" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="O1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="P1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="Q1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>

--- a/input.xlsx
+++ b/input.xlsx
@@ -39,7 +39,7 @@
     <t>Test IDs</t>
   </si>
   <si>
-    <t>https://www.gehealthcare.com/</t>
+    <t>https://www.gehealthcare.com/en-us</t>
   </si>
   <si>
     <t>USA</t>
@@ -48,58 +48,58 @@
     <t>TC-01,TC-02,TC-03,TC-04,TC-05,TC-06,TC-09,TC-14</t>
   </si>
   <si>
-    <t>https://www.gehealthcare.com/products/imaging</t>
+    <t>https://www.gehealthcare.com/en-us/products/imaging</t>
   </si>
   <si>
     <t>TC-03,TC-04,TC-05,TC-06,TC-09,TC-14</t>
   </si>
   <si>
-    <t>https://www.gehealthcare.com/products/bone-and-metabolic-health</t>
+    <t>https://www.gehealthcare.com/en-us/products/bone-and-metabolic-health</t>
   </si>
   <si>
     <t>TC-03,TC-04,TC-05,TC-06,TC-08,TC-09,TC-14</t>
   </si>
   <si>
-    <t>https://www.gehealthcare.com/products/ultrasound</t>
+    <t>https://www.gehealthcare.com/en-us/products/ultrasound</t>
   </si>
   <si>
     <t>TC-03,TC-04,TC-05,TC-06,TC-07,TC-09,TC-14</t>
   </si>
   <si>
-    <t>https://www.gehealthcare.com/products/ultrasound/voluson</t>
-  </si>
-  <si>
-    <t>https://www.gehealthcare.com/products/patient-care-solutions</t>
-  </si>
-  <si>
-    <t>https://www.gehealthcare.com/products/patient-monitoring</t>
-  </si>
-  <si>
-    <t>https://www.gehealthcare.com/products/molecular-imaging-agents</t>
+    <t>https://www.gehealthcare.com/en-us/products/ultrasound/voluson</t>
+  </si>
+  <si>
+    <t>https://www.gehealthcare.com/en-us/products/patient-care-solutions</t>
+  </si>
+  <si>
+    <t>https://www.gehealthcare.com/en-us/products/patient-monitoring</t>
+  </si>
+  <si>
+    <t>https://www.gehealthcare.com/en-us/products/molecular-imaging-agents</t>
   </si>
   <si>
     <t>TC-03,TC-04,TC-05,TC-06,TC-10,TC-09,TC-14</t>
   </si>
   <si>
-    <t>https://www.gehealthcare.com/products/molecular-imaging-agents/cerianna</t>
-  </si>
-  <si>
-    <t>https://www.gehealthcare.com/products/contrast-media</t>
-  </si>
-  <si>
-    <t>https://www.gehealthcare.com/products/contrast-media/omnipaque</t>
-  </si>
-  <si>
-    <t>https://www.gehealthcare.com/insights?showPopup=false</t>
+    <t>https://www.gehealthcare.com/en-us/products/molecular-imaging-agents/cerianna</t>
+  </si>
+  <si>
+    <t>https://www.gehealthcare.com/en-us/products/contrast-media</t>
+  </si>
+  <si>
+    <t>https://www.gehealthcare.com/en-us/products/contrast-media/omnipaque</t>
+  </si>
+  <si>
+    <t>https://www.gehealthcare.com/en-us/insights?showPopup=false</t>
   </si>
   <si>
     <t>TC-03,TC-04,TC-05,TC-06,TC-11,TC-09,TC-14</t>
   </si>
   <si>
-    <t>https://www.gehealthcare.com/about/newsroom</t>
-  </si>
-  <si>
-    <t>https://www.gehealthcare.com/en-gb/</t>
+    <t>https://www.gehealthcare.com/en-us/about/newsroom</t>
+  </si>
+  <si>
+    <t>https://www.gehealthcare.com/en-gb</t>
   </si>
   <si>
     <t>UK</t>
@@ -138,7 +138,7 @@
     <t>https://www.gehealthcare.com/en-gb/insights</t>
   </si>
   <si>
-    <t>https://www.gehealthcare.com/de-de/</t>
+    <t>https://www.gehealthcare.com/de-de</t>
   </si>
   <si>
     <t>DE</t>
@@ -177,16 +177,16 @@
     <t>FR</t>
   </si>
   <si>
-    <t>https://www.gehealthcare.fr/products/imaging</t>
-  </si>
-  <si>
-    <t>https://www.gehealthcare.fr/products/magnetic-resonance-imaging</t>
+    <t>https://www.gehealthcare.com/fr-fr/products/imaging</t>
+  </si>
+  <si>
+    <t>https://www.gehealthcare.com/fr-fr/products/magnetic-resonance-imaging</t>
   </si>
   <si>
     <t>https://www.gehealthcare.fr/products/ultrasound</t>
   </si>
   <si>
-    <t>https://www.gehealthcare.fr/insights/articles</t>
+    <t>https://www.gehealthcare.com/fr-fr/insights/articles</t>
   </si>
   <si>
     <t>https://www.gehealthcare.in/</t>
@@ -195,34 +195,34 @@
     <t>IN</t>
   </si>
   <si>
-    <t>https://www.gehealthcare.in/products/imaging</t>
-  </si>
-  <si>
-    <t>https://www.gehealthcare.in/products/computed-tomography</t>
-  </si>
-  <si>
-    <t>https://www.gehealthcare.in/products/ultrasound</t>
-  </si>
-  <si>
-    <t>https://www.gehealthcare.in/products/ultrasound/logiq</t>
-  </si>
-  <si>
-    <t>https://www.gehealthcare.in/products/contrast-media</t>
-  </si>
-  <si>
-    <t>https://www.gehealthcare.in/products/contrast-media/omnipaque</t>
+    <t>https://www.gehealthcare.com/en-in/products/imaging</t>
+  </si>
+  <si>
+    <t>https://www.gehealthcare.com/en-in/products/computed-tomography</t>
+  </si>
+  <si>
+    <t>https://www.gehealthcare.com/en-in/products/ultrasound</t>
+  </si>
+  <si>
+    <t>https://www.gehealthcare.com/en-in/products/ultrasound/logiq</t>
+  </si>
+  <si>
+    <t>https://www.gehealthcare.com/en-in/products/contrast-media</t>
+  </si>
+  <si>
+    <t>https://www.gehealthcare.com/en-in/products/contrast-media/omnipaque</t>
   </si>
   <si>
     <t>https://www.gehealthcare.in/insights?showPopup=false</t>
   </si>
   <si>
-    <t>https://www.gehealthcare.in/about/newsroom</t>
-  </si>
-  <si>
-    <t>https://www.gehealthcare.in/products/anesthesia-delivery</t>
-  </si>
-  <si>
-    <t>https://www.gehealthcare.in/products/diagnostic-ecg</t>
+    <t>https://www.gehealthcare.com/en-in/about/newsroom</t>
+  </si>
+  <si>
+    <t>https://www.gehealthcare.com/en-in/products/anesthesia-delivery</t>
+  </si>
+  <si>
+    <t>https://www.gehealthcare.com/en-in/products/diagnostic-cardiology</t>
   </si>
   <si>
     <t>TC-01</t>

--- a/input.xlsx
+++ b/input.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="87">
   <si>
     <t>Run Date</t>
   </si>
@@ -156,6 +156,9 @@
     <t>https://www.gehealthcare.com/de-de/products/nuclear-imaging-agents/datscan</t>
   </si>
   <si>
+    <t>TC-14,TC-15</t>
+  </si>
+  <si>
     <t>https://www.gehealthcare.com/de-de/insights/articles</t>
   </si>
   <si>
@@ -183,7 +186,10 @@
     <t>https://www.gehealthcare.com/fr-fr/products/magnetic-resonance-imaging</t>
   </si>
   <si>
-    <t>https://www.gehealthcare.fr/products/ultrasound</t>
+    <t>https://gehealthcare-ultrasound.com/fr/</t>
+  </si>
+  <si>
+    <t>TC-14,TC-16</t>
   </si>
   <si>
     <t>https://www.gehealthcare.com/fr-fr/insights/articles</t>
@@ -1017,12 +1023,12 @@
         <v>41</v>
       </c>
       <c r="C30" t="s">
-        <v>11</v>
+        <v>46</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B31" t="s">
         <v>41</v>
@@ -1033,7 +1039,7 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B32" t="s">
         <v>41</v>
@@ -1044,7 +1050,7 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B33" t="s">
         <v>41</v>
@@ -1055,7 +1061,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B34" t="s">
         <v>41</v>
@@ -1066,7 +1072,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B35" t="s">
         <v>41</v>
@@ -1077,10 +1083,10 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B36" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C36" t="s">
         <v>9</v>
@@ -1088,10 +1094,10 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>54</v>
+      </c>
+      <c r="B37" t="s">
         <v>53</v>
-      </c>
-      <c r="B37" t="s">
-        <v>52</v>
       </c>
       <c r="C37" t="s">
         <v>11</v>
@@ -1099,10 +1105,10 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B38" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C38" t="s">
         <v>13</v>
@@ -1110,21 +1116,21 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B39" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C39" t="s">
-        <v>11</v>
+        <v>57</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B40" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C40" t="s">
         <v>11</v>
@@ -1132,10 +1138,10 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B41" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C41" t="s">
         <v>9</v>
@@ -1143,10 +1149,10 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B42" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C42" t="s">
         <v>11</v>
@@ -1154,10 +1160,10 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>62</v>
+      </c>
+      <c r="B43" t="s">
         <v>60</v>
-      </c>
-      <c r="B43" t="s">
-        <v>58</v>
       </c>
       <c r="C43" t="s">
         <v>13</v>
@@ -1165,10 +1171,10 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B44" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C44" t="s">
         <v>11</v>
@@ -1176,10 +1182,10 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B45" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C45" t="s">
         <v>13</v>
@@ -1187,10 +1193,10 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B46" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C46" t="s">
         <v>11</v>
@@ -1198,10 +1204,10 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B47" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C47" t="s">
         <v>11</v>
@@ -1209,10 +1215,10 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B48" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C48" t="s">
         <v>25</v>
@@ -1220,10 +1226,10 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B49" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C49" t="s">
         <v>25</v>
@@ -1231,10 +1237,10 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B50" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C50" t="s">
         <v>11</v>
@@ -1242,10 +1248,10 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B51" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C51" t="s">
         <v>11</v>
@@ -1274,52 +1280,52 @@
         <v>4</v>
       </c>
       <c r="B1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="J1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="K1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="L1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="M1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="N1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="O1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="P1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="Q1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
